--- a/docs/downloads/经营分_鲁西省区__济宁片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_鲁西省区__济宁片区_2026-10-18.xlsx
@@ -546,7 +546,7 @@
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
@@ -1303,17 +1303,17 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>6601131679065049095</t>
+          <t>7317873242444662825</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>锦江之星（济宁兖州世纪银座广场酒店）</t>
+          <t>锦江之星（泗水县仲庙文化路酒店）</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>锦江之星(济宁兖州世纪银座广场店)</t>
+          <t>锦江之星(泗水县仲庙文化路店)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1391,22 +1391,22 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>6693202627557197832</t>
+          <t>6601131679065049095</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>非繁云居酒店(曲阜三孔风景区店)</t>
+          <t>锦江之星（济宁兖州世纪银座广场酒店）</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>非繁云居酒店(曲阜三孔风景区店)</t>
+          <t>锦江之星(济宁兖州世纪银座广场店)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1433,13 +1433,13 @@
         <v>30</v>
       </c>
       <c r="O10" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P10" t="n">
         <v>30</v>
       </c>
       <c r="Q10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R10" t="n">
         <v>30</v>
@@ -1479,33 +1479,33 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>6852725330684184580</t>
+          <t>6693202627557197832</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>IU酒店（曲阜孔庙南门大街店）</t>
+          <t>非繁云居酒店(曲阜三孔风景区店)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>iu酒店(曲阜孔庙南门大街店)</t>
+          <t>非繁云居酒店(曲阜三孔风景区店)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1515,19 +1515,19 @@
         <v>10</v>
       </c>
       <c r="M11" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N11" t="n">
         <v>30</v>
       </c>
       <c r="O11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P11" t="n">
         <v>30</v>
       </c>
       <c r="Q11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R11" t="n">
         <v>30</v>
@@ -1567,33 +1567,33 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>7046318945619740708</t>
+          <t>7265988533893761076</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店(曲阜师范大学店)</t>
+          <t>麗枫酒店（济宁济州上城店）</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>白玉兰酒店(曲阜师范大学店)</t>
+          <t>麗枫酒店(济宁济州上城店)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I12" t="n">
         <v>-5</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1603,19 +1603,19 @@
         <v>10</v>
       </c>
       <c r="M12" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N12" t="n">
         <v>30</v>
       </c>
       <c r="O12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P12" t="n">
         <v>30</v>
       </c>
       <c r="Q12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R12" t="n">
         <v>30</v>
@@ -1655,17 +1655,17 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>6903641003169679371</t>
+          <t>6852725330684184580</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店（济宁济邹路济州上城店）</t>
+          <t>IU酒店（曲阜孔庙南门大街店）</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店(济宁济邹路济州上城店)</t>
+          <t>iu酒店(曲阜孔庙南门大街店)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1677,11 +1677,11 @@
         <v>100</v>
       </c>
       <c r="I13" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1691,19 +1691,19 @@
         <v>10</v>
       </c>
       <c r="M13" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N13" t="n">
         <v>30</v>
       </c>
       <c r="O13" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P13" t="n">
         <v>30</v>
       </c>
       <c r="Q13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R13" t="n">
         <v>30</v>
@@ -1743,29 +1743,29 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>7227382775228139581</t>
+          <t>7046318945619740708</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>维也纳3好酒店（曲阜高铁东站店）</t>
+          <t>白玉兰商务酒店(曲阜师范大学店)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>维也纳3好酒店(曲阜高铁东站店)</t>
+          <t>白玉兰酒店(曲阜师范大学店)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H14" t="n">
         <v>100</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1831,33 +1831,33 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>6601196088412080142</t>
+          <t>6903641003169679371</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（山东济宁高新区杨柳国际新城店）</t>
+          <t>白玉兰商务酒店（济宁济邹路济州上城店）</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(山东济宁高新区杨柳国际新城店)</t>
+          <t>白玉兰商务酒店(济宁济邹路济州上城店)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H15" t="n">
         <v>100</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1867,19 +1867,19 @@
         <v>10</v>
       </c>
       <c r="M15" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N15" t="n">
         <v>30</v>
       </c>
       <c r="O15" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P15" t="n">
         <v>30</v>
       </c>
       <c r="Q15" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R15" t="n">
         <v>30</v>
@@ -1919,22 +1919,22 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>6601136116881950727</t>
+          <t>7227382775228139581</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>锦江之星品尚（济宁济州上城火炬南路酒店）</t>
+          <t>维也纳3好酒店（曲阜高铁东站店）</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>锦江之星品尚(济宁济州上城火炬南路酒店)</t>
+          <t>维也纳3好酒店(曲阜高铁东站店)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1955,13 +1955,13 @@
         <v>10</v>
       </c>
       <c r="M16" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N16" t="n">
         <v>30</v>
       </c>
       <c r="O16" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P16" t="n">
         <v>30</v>
@@ -2007,33 +2007,33 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>7317873242444662825</t>
+          <t>6601196088412080142</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>锦江之星（泗水县仲庙文化路酒店）</t>
+          <t>维也纳国际酒店（山东济宁高新区杨柳国际新城店）</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>锦江之星(泗水县仲庙文化路店)</t>
+          <t>维也纳国际酒店(山东济宁高新区杨柳国际新城店)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H17" t="n">
         <v>100</v>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -2043,7 +2043,7 @@
         <v>10</v>
       </c>
       <c r="M17" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N17" t="n">
         <v>30</v>
@@ -2055,7 +2055,7 @@
         <v>30</v>
       </c>
       <c r="Q17" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R17" t="n">
         <v>30</v>
@@ -2095,22 +2095,22 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>7235876853452376067</t>
+          <t>6601136116881950727</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>麗枫酒店（曲阜三孔景区店）</t>
+          <t>锦江之星品尚（济宁济州上城火炬南路酒店）</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>麗枫酒店(曲阜三孔景区店)</t>
+          <t>锦江之星品尚(济宁济州上城火炬南路酒店)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -2131,13 +2131,13 @@
         <v>10</v>
       </c>
       <c r="M18" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N18" t="n">
         <v>30</v>
       </c>
       <c r="O18" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P18" t="n">
         <v>30</v>
@@ -2183,17 +2183,17 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>7265988533893761076</t>
+          <t>7235876853452376067</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>麗枫酒店（济宁济州上城店）</t>
+          <t>麗枫酒店（曲阜三孔景区店）</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>麗枫酒店(济宁济州上城店)</t>
+          <t>麗枫酒店(曲阜三孔景区店)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -2219,19 +2219,19 @@
         <v>10</v>
       </c>
       <c r="M19" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N19" t="n">
         <v>30</v>
       </c>
       <c r="O19" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P19" t="n">
         <v>30</v>
       </c>
       <c r="Q19" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R19" t="n">
         <v>30</v>
@@ -2271,17 +2271,17 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>7279413652925450276</t>
+          <t>7150978574298646531</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>维也纳酒店（曲阜三孔风景店）</t>
+          <t>IU酒店·山东济宁微山奎文东路店</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>维也纳酒店(曲阜三孔风景店)</t>
+          <t>IU酒店(山东济宁微山奎文东路店)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2290,30 +2290,30 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="I20" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>搭门店,稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L20" t="n">
         <v>10</v>
       </c>
       <c r="M20" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N20" t="n">
         <v>30</v>
       </c>
       <c r="O20" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P20" t="n">
         <v>30</v>
@@ -2359,17 +2359,17 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>7150978574298646531</t>
+          <t>7454879495514753076</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>IU酒店·山东济宁微山奎文东路店</t>
+          <t>凯里亚德酒店(3.0版济宁任城区政府龙贵广场店)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>IU酒店(山东济宁微山奎文东路店)</t>
+          <t>凯里亚德酒店(济宁任城区龙贵广场店)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2381,7 +2381,7 @@
         <v>105</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -2401,13 +2401,13 @@
         <v>30</v>
       </c>
       <c r="O21" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P21" t="n">
         <v>30</v>
       </c>
       <c r="Q21" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R21" t="n">
         <v>30</v>
@@ -2447,17 +2447,17 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>7454879495514753076</t>
+          <t>7517226069750745103</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>凯里亚德酒店(3.0版济宁任城区政府龙贵广场店)</t>
+          <t>希岸酒店（曲阜三孔景区店）</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>凯里亚德酒店(济宁任城区龙贵广场店)</t>
+          <t>希岸酒店(曲阜三孔景区店)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2469,7 +2469,7 @@
         <v>105</v>
       </c>
       <c r="I22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -2535,17 +2535,17 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>7517226069750745103</t>
+          <t>7369781101101615158</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>希岸酒店（曲阜三孔景区店）</t>
+          <t>白玉兰商务酒店（济宁万达广场店）</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>希岸酒店(曲阜三孔景区店)</t>
+          <t>白玉兰酒店(济宁万达广场店)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -2571,13 +2571,13 @@
         <v>10</v>
       </c>
       <c r="M23" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N23" t="n">
         <v>30</v>
       </c>
       <c r="O23" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P23" t="n">
         <v>30</v>
@@ -2623,22 +2623,22 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>7369781101101615158</t>
+          <t>7278638102695675915</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店（济宁万达广场店）</t>
+          <t>白玉兰酒店（兖州火车站酒仙桥南路店）</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>白玉兰酒店(济宁万达广场店)</t>
+          <t>白玉兰酒店(济宁兖州火车站酒仙桥南路店)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -2711,17 +2711,17 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>7278638102695675915</t>
+          <t>7103375503024883748</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>白玉兰酒店（兖州火车站酒仙桥南路店）</t>
+          <t>维也纳国际酒店（济宁任城区政务中心店）</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>白玉兰酒店(济宁兖州火车站酒仙桥南路店)</t>
+          <t>维也纳国际酒店(济宁任城区政务中心店)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>拿收益</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -2747,7 +2747,7 @@
         <v>10</v>
       </c>
       <c r="M25" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N25" t="n">
         <v>30</v>
@@ -2759,7 +2759,7 @@
         <v>30</v>
       </c>
       <c r="Q25" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R25" t="n">
         <v>30</v>
@@ -2799,17 +2799,17 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>7103375503024883748</t>
+          <t>7555113289936537646</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（济宁任城区政务中心店）</t>
+          <t>锦江之星（曲阜富良商城三孔景区店）</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(济宁任城区政务中心店)</t>
+          <t>锦江之星酒店(曲阜三孔景区店)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -2841,13 +2841,13 @@
         <v>30</v>
       </c>
       <c r="O26" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P26" t="n">
         <v>30</v>
       </c>
       <c r="Q26" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R26" t="n">
         <v>30</v>
@@ -2887,55 +2887,55 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>7555113289936537646</t>
+          <t>7279413652925450276</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>锦江之星（曲阜富良商城三孔景区店）</t>
+          <t>维也纳酒店（曲阜三孔风景店）</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>锦江之星酒店(曲阜三孔景区店)</t>
+          <t>维也纳酒店(曲阜三孔风景店)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>搭门店,稳房源,拿收益</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L27" t="n">
         <v>10</v>
       </c>
       <c r="M27" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N27" t="n">
         <v>30</v>
       </c>
       <c r="O27" t="n">
+        <v>30</v>
+      </c>
+      <c r="P27" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q27" t="n">
         <v>25</v>
-      </c>
-      <c r="P27" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>20</v>
       </c>
       <c r="R27" t="n">
         <v>30</v>
